--- a/data/sample_commercial_data.xlsx
+++ b/data/sample_commercial_data.xlsx
@@ -484,7 +484,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44929</v>
+        <v>45659</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44930</v>
+        <v>45660</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44930</v>
+        <v>45660</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44931</v>
+        <v>45661</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44935</v>
+        <v>45664</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44937</v>
+        <v>45665</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44942</v>
+        <v>45668</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44944</v>
+        <v>45670</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44944</v>
+        <v>45670</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44949</v>
+        <v>45673</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44956</v>
+        <v>45678</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44958</v>
+        <v>45679</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44959</v>
+        <v>45680</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44959</v>
+        <v>45680</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44960</v>
+        <v>45681</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44961</v>
+        <v>45681</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1252,11 +1252,11 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44967</v>
+        <v>45686</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Consumer Health Simulation</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LabReady Pro</t>
+          <t>WellnessSet Pro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1280,31 +1280,31 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>74964.44</v>
+        <v>26903.79</v>
       </c>
       <c r="H18" t="n">
-        <v>65177.74</v>
+        <v>23293.59</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0835</v>
+        <v>0.2398</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44968</v>
+        <v>45686</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Consumer Health Simulation</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>WellnessSet Pro</t>
+          <t>LabReady Pro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1328,27 +1328,27 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>26903.79</v>
+        <v>74964.44</v>
       </c>
       <c r="H19" t="n">
-        <v>23293.59</v>
+        <v>65177.74</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2398</v>
+        <v>0.0835</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>44968</v>
+        <v>45686</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>44971</v>
+        <v>45688</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>44971</v>
+        <v>45688</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>44971</v>
+        <v>45688</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>44974</v>
+        <v>45690</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>44975</v>
+        <v>45691</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>44976</v>
+        <v>45692</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>44978</v>
+        <v>45693</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>44978</v>
+        <v>45693</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>44981</v>
+        <v>45695</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>44984</v>
+        <v>45698</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>44986</v>
+        <v>45699</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>44987</v>
+        <v>45699</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>44988</v>
+        <v>45700</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>44989</v>
+        <v>45700</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>44989</v>
+        <v>45701</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>44990</v>
+        <v>45701</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>44991</v>
+        <v>45702</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>44992</v>
+        <v>45703</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>44992</v>
+        <v>45703</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>44992</v>
+        <v>45703</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>44995</v>
+        <v>45705</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>44995</v>
+        <v>45705</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>44996</v>
+        <v>45706</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2500,103 +2500,103 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>44999</v>
+        <v>45707</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Consumer Health Simulation</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>WellnessSet Pro</t>
+          <t>IV FlowMaster</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fabio Lima</t>
+          <t>Bruno Martins</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>78515.36</v>
+        <v>43135.46</v>
       </c>
       <c r="H44" t="n">
-        <v>83543.5</v>
+        <v>49092.23</v>
       </c>
       <c r="I44" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="J44" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="L44" t="n">
-        <v>0.1541</v>
+        <v>0.0367</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>44999</v>
+        <v>45708</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Consumer Health Simulation</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IV FlowMaster</t>
+          <t>WellnessSet Pro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bruno Martins</t>
+          <t>Fabio Lima</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>43135.46</v>
+        <v>78515.36</v>
       </c>
       <c r="H45" t="n">
-        <v>49092.23</v>
+        <v>83543.5</v>
       </c>
       <c r="I45" t="n">
+        <v>36</v>
+      </c>
+      <c r="J45" t="n">
+        <v>19</v>
+      </c>
+      <c r="K45" t="n">
         <v>6</v>
       </c>
-      <c r="J45" t="n">
-        <v>3</v>
-      </c>
-      <c r="K45" t="n">
-        <v>17</v>
-      </c>
       <c r="L45" t="n">
-        <v>0.0367</v>
+        <v>0.1541</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45004</v>
+        <v>45711</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45005</v>
+        <v>45712</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45008</v>
+        <v>45714</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45008</v>
+        <v>45714</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45008</v>
+        <v>45714</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45010</v>
+        <v>45715</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45010</v>
+        <v>45715</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2932,11 +2932,11 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45012</v>
+        <v>45717</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2946,45 +2946,45 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IV FlowMaster</t>
+          <t>DiagnoKit Elite</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Elena Costa</t>
+          <t>Fabio Lima</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>59240</v>
+        <v>25718.49</v>
       </c>
       <c r="H53" t="n">
-        <v>60342.89</v>
+        <v>25476.26</v>
       </c>
       <c r="I53" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="K53" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2455</v>
+        <v>0.1516</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45013</v>
+        <v>45717</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2994,41 +2994,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DiagnoKit Elite</t>
+          <t>IV FlowMaster</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fabio Lima</t>
+          <t>Elena Costa</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>25718.49</v>
+        <v>59240</v>
       </c>
       <c r="H54" t="n">
-        <v>25476.26</v>
+        <v>60342.89</v>
       </c>
       <c r="I54" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="J54" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="K54" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="L54" t="n">
-        <v>0.1516</v>
+        <v>0.2455</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45014</v>
+        <v>45718</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45019</v>
+        <v>45721</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45020</v>
+        <v>45722</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45023</v>
+        <v>45724</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45024</v>
+        <v>45725</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45028</v>
+        <v>45728</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45029</v>
+        <v>45728</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45032</v>
+        <v>45730</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45035</v>
+        <v>45733</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45037</v>
+        <v>45734</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45038</v>
+        <v>45735</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45039</v>
+        <v>45735</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45043</v>
+        <v>45738</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>45047</v>
+        <v>45741</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>45047</v>
+        <v>45741</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>45047</v>
+        <v>45741</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>45052</v>
+        <v>45745</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>45054</v>
+        <v>45745</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3892,16 +3892,16 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>45054</v>
+        <v>45746</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3911,36 +3911,36 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>WoundShield</t>
+          <t>BedCare System</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gabriela Rocha</t>
+          <t>Carla Oliveira</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>11909.33</v>
+        <v>75210.5</v>
       </c>
       <c r="H73" t="n">
-        <v>12947.59</v>
+        <v>84469.33</v>
       </c>
       <c r="I73" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K73" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="L73" t="n">
-        <v>0.1266</v>
+        <v>0.0941</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>45054</v>
+        <v>45746</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3949,94 +3949,94 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FlexCath Pro</t>
+          <t>WoundShield</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Gabriela Rocha</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>47475.24</v>
+        <v>11909.33</v>
       </c>
       <c r="H74" t="n">
-        <v>47138.79</v>
+        <v>12947.59</v>
       </c>
       <c r="I74" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J74" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K74" t="n">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="L74" t="n">
-        <v>0.0834</v>
+        <v>0.1266</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>45055</v>
+        <v>45746</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BedCare System</t>
+          <t>FlexCath Pro</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Carla Oliveira</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>75210.5</v>
+        <v>47475.24</v>
       </c>
       <c r="H75" t="n">
-        <v>84469.33</v>
+        <v>47138.79</v>
       </c>
       <c r="I75" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K75" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="L75" t="n">
-        <v>0.0941</v>
+        <v>0.0834</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>45056</v>
+        <v>45747</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>45058</v>
+        <v>45748</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>45058</v>
+        <v>45748</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>45062</v>
+        <v>45751</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>45062</v>
+        <v>45751</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>45065</v>
+        <v>45753</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>45065</v>
+        <v>45753</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>45068</v>
+        <v>45755</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>45069</v>
+        <v>45756</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>45072</v>
+        <v>45758</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>45079</v>
+        <v>45763</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>45090</v>
+        <v>45770</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>45090</v>
+        <v>45770</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>45090</v>
+        <v>45770</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>45091</v>
+        <v>45771</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>45094</v>
+        <v>45773</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>45096</v>
+        <v>45775</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>45097</v>
+        <v>45775</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>45101</v>
+        <v>45778</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>45103</v>
+        <v>45780</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>45105</v>
+        <v>45781</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>45105</v>
+        <v>45781</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>45106</v>
+        <v>45782</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>45108</v>
+        <v>45783</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>45109</v>
+        <v>45783</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>45111</v>
+        <v>45785</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>45115</v>
+        <v>45788</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>45117</v>
+        <v>45789</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>45120</v>
+        <v>45791</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -5394,41 +5394,41 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Patient Care</t>
+          <t>Consumer Health Simulation</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ComfortBrace</t>
+          <t>CareSimPack</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Elena Costa</t>
+          <t>Henrique Silva</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>21962.21</v>
+        <v>6867.83</v>
       </c>
       <c r="H104" t="n">
-        <v>25270.69</v>
+        <v>8224.77</v>
       </c>
       <c r="I104" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J104" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K104" t="n">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="L104" t="n">
-        <v>0.053</v>
+        <v>0.0317</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>45120</v>
+        <v>45792</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -5442,41 +5442,41 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Consumer Health Simulation</t>
+          <t>Patient Care</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CareSimPack</t>
+          <t>ComfortBrace</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Henrique Silva</t>
+          <t>Elena Costa</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>6867.83</v>
+        <v>21962.21</v>
       </c>
       <c r="H105" t="n">
-        <v>8224.77</v>
+        <v>25270.69</v>
       </c>
       <c r="I105" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J105" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K105" t="n">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="L105" t="n">
-        <v>0.0317</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>45121</v>
+        <v>45792</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>45122</v>
+        <v>45793</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>45123</v>
+        <v>45793</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>45127</v>
+        <v>45796</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>45128</v>
+        <v>45797</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>45129</v>
+        <v>45797</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>45131</v>
+        <v>45799</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>45131</v>
+        <v>45799</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>45132</v>
+        <v>45799</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>45133</v>
+        <v>45800</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>45137</v>
+        <v>45803</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>45137</v>
+        <v>45803</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>45138</v>
+        <v>45804</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>45138</v>
+        <v>45804</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>45139</v>
+        <v>45805</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -6196,103 +6196,103 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>45141</v>
+        <v>45806</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>HospCore Suite</t>
+          <t>FlexCath Pro</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Isabela Ferreira</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>21109.5</v>
+        <v>76891.94</v>
       </c>
       <c r="H121" t="n">
-        <v>18427.24</v>
+        <v>78337.99000000001</v>
       </c>
       <c r="I121" t="n">
         <v>6</v>
       </c>
       <c r="J121" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K121" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="L121" t="n">
-        <v>0.129</v>
+        <v>0.0207</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>45142</v>
+        <v>45806</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FlexCath Pro</t>
+          <t>HospCore Suite</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Isabela Ferreira</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>76891.94</v>
+        <v>21109.5</v>
       </c>
       <c r="H122" t="n">
-        <v>78337.99000000001</v>
+        <v>18427.24</v>
       </c>
       <c r="I122" t="n">
         <v>6</v>
       </c>
       <c r="J122" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K122" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L122" t="n">
-        <v>0.0207</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>45143</v>
+        <v>45807</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>45145</v>
+        <v>45808</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>45147</v>
+        <v>45810</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>45148</v>
+        <v>45810</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>45150</v>
+        <v>45812</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -6532,107 +6532,107 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>45154</v>
+        <v>45815</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>WoundShield</t>
+          <t>OrthoFix Plus</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Isabela Ferreira</t>
+          <t>Bruno Martins</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>74591.75</v>
+        <v>70753.31</v>
       </c>
       <c r="H128" t="n">
-        <v>66470.69</v>
+        <v>82468.25999999999</v>
       </c>
       <c r="I128" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="J128" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K128" t="n">
-        <v>6</v>
+        <v>98</v>
       </c>
       <c r="L128" t="n">
-        <v>0.2087</v>
+        <v>0.2456</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>45155</v>
+        <v>45815</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>OrthoFix Plus</t>
+          <t>WoundShield</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bruno Martins</t>
+          <t>Isabela Ferreira</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>70753.31</v>
+        <v>74591.75</v>
       </c>
       <c r="H129" t="n">
-        <v>82468.25999999999</v>
+        <v>66470.69</v>
       </c>
       <c r="I129" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="J129" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K129" t="n">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="L129" t="n">
-        <v>0.2456</v>
+        <v>0.2087</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>45160</v>
+        <v>45819</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6642,45 +6642,45 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Consumer Health Simulation</t>
+          <t>Patient Care</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>WellnessSet Pro</t>
+          <t>RecoverEase</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bruno Martins</t>
+          <t>Carla Oliveira</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>55426.93</v>
+        <v>103181.24</v>
       </c>
       <c r="H130" t="n">
-        <v>55353.32</v>
+        <v>96017.87</v>
       </c>
       <c r="I130" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J130" t="n">
+        <v>3</v>
+      </c>
+      <c r="K130" t="n">
         <v>4</v>
       </c>
-      <c r="K130" t="n">
-        <v>6</v>
-      </c>
       <c r="L130" t="n">
-        <v>0.1681</v>
+        <v>0.1387</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>45161</v>
+        <v>45819</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6690,41 +6690,41 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Patient Care</t>
+          <t>Consumer Health Simulation</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RecoverEase</t>
+          <t>WellnessSet Pro</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Carla Oliveira</t>
+          <t>Bruno Martins</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>103181.24</v>
+        <v>55426.93</v>
       </c>
       <c r="H131" t="n">
-        <v>96017.87</v>
+        <v>55353.32</v>
       </c>
       <c r="I131" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K131" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L131" t="n">
-        <v>0.1387</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>45164</v>
+        <v>45822</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>45166</v>
+        <v>45823</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>45170</v>
+        <v>45826</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>45171</v>
+        <v>45827</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>45173</v>
+        <v>45828</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>45174</v>
+        <v>45828</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>45175</v>
+        <v>45829</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>45176</v>
+        <v>45830</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>45177</v>
+        <v>45831</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -7156,103 +7156,103 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>45177</v>
+        <v>45831</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>WoundShield</t>
+          <t>DiagnoKit Elite</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Isabela Ferreira</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>84016.96000000001</v>
+        <v>20762.58</v>
       </c>
       <c r="H141" t="n">
-        <v>97243.58</v>
+        <v>23111.31</v>
       </c>
       <c r="I141" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J141" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="K141" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L141" t="n">
-        <v>0.1293</v>
+        <v>0.0682</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>45177</v>
+        <v>45831</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>DiagnoKit Elite</t>
+          <t>WoundShield</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Isabela Ferreira</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>20762.58</v>
+        <v>84016.96000000001</v>
       </c>
       <c r="H142" t="n">
-        <v>23111.31</v>
+        <v>97243.58</v>
       </c>
       <c r="I142" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J142" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K142" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L142" t="n">
-        <v>0.0682</v>
+        <v>0.1293</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>45182</v>
+        <v>45834</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>45186</v>
+        <v>45837</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>45188</v>
+        <v>45838</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -7396,103 +7396,103 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>45188</v>
+        <v>45839</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Patient Care</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RecoverEase</t>
+          <t>IV FlowMaster</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Henrique Silva</t>
+          <t>Bruno Martins</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>12195.21</v>
+        <v>30514.29</v>
       </c>
       <c r="H146" t="n">
-        <v>10433.39</v>
+        <v>29001.16</v>
       </c>
       <c r="I146" t="n">
+        <v>49</v>
+      </c>
+      <c r="J146" t="n">
+        <v>18</v>
+      </c>
+      <c r="K146" t="n">
         <v>25</v>
       </c>
-      <c r="J146" t="n">
-        <v>15</v>
-      </c>
-      <c r="K146" t="n">
-        <v>48</v>
-      </c>
       <c r="L146" t="n">
-        <v>0.1236</v>
+        <v>0.06569999999999999</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>45189</v>
+        <v>45839</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Patient Care</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>IV FlowMaster</t>
+          <t>RecoverEase</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bruno Martins</t>
+          <t>Henrique Silva</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>30514.29</v>
+        <v>12195.21</v>
       </c>
       <c r="H147" t="n">
-        <v>29001.16</v>
+        <v>10433.39</v>
       </c>
       <c r="I147" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="J147" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K147" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="L147" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.1236</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>45191</v>
+        <v>45840</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -7501,46 +7501,46 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>IV FlowMaster</t>
+          <t>OrthoFix Plus</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Henrique Silva</t>
+          <t>Isabela Ferreira</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>19272.82</v>
+        <v>20920.79</v>
       </c>
       <c r="H148" t="n">
-        <v>21886.59</v>
+        <v>24332.53</v>
       </c>
       <c r="I148" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="J148" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K148" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="L148" t="n">
-        <v>0.0419</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>45191</v>
+        <v>45841</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -7549,46 +7549,46 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>OrthoFix Plus</t>
+          <t>IV FlowMaster</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Isabela Ferreira</t>
+          <t>Henrique Silva</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>20920.79</v>
+        <v>19272.82</v>
       </c>
       <c r="H149" t="n">
-        <v>24332.53</v>
+        <v>21886.59</v>
       </c>
       <c r="I149" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="J149" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K149" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="L149" t="n">
-        <v>0.043</v>
+        <v>0.0419</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>45192</v>
+        <v>45841</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -7636,16 +7636,16 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>45193</v>
+        <v>45842</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FlexCath Pro</t>
+          <t>OrthoFix Plus</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7664,36 +7664,36 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>41702.79</v>
+        <v>27188.77</v>
       </c>
       <c r="H151" t="n">
-        <v>39869.44</v>
+        <v>30699.62</v>
       </c>
       <c r="I151" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J151" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K151" t="n">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="L151" t="n">
-        <v>0.059</v>
+        <v>0.0346</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>45194</v>
+        <v>45842</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>OrthoFix Plus</t>
+          <t>FlexCath Pro</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7712,27 +7712,27 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>27188.77</v>
+        <v>41702.79</v>
       </c>
       <c r="H152" t="n">
-        <v>30699.62</v>
+        <v>39869.44</v>
       </c>
       <c r="I152" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J152" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K152" t="n">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="L152" t="n">
-        <v>0.0346</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>45194</v>
+        <v>45842</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -7780,11 +7780,11 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>45196</v>
+        <v>45844</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7794,41 +7794,41 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>DiagnoKit Elite</t>
+          <t>WoundShield</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bruno Martins</t>
+          <t>Carla Oliveira</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>44518.34</v>
+        <v>58573.13</v>
       </c>
       <c r="H154" t="n">
-        <v>48954.16</v>
+        <v>61823.55</v>
       </c>
       <c r="I154" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="J154" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K154" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="L154" t="n">
-        <v>0.2164</v>
+        <v>0.0851</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>45196</v>
+        <v>45844</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -7876,11 +7876,11 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>45197</v>
+        <v>45844</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7890,41 +7890,41 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>WoundShield</t>
+          <t>DiagnoKit Elite</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Carla Oliveira</t>
+          <t>Bruno Martins</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>58573.13</v>
+        <v>44518.34</v>
       </c>
       <c r="H156" t="n">
-        <v>61823.55</v>
+        <v>48954.16</v>
       </c>
       <c r="I156" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="J156" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K156" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="L156" t="n">
-        <v>0.0851</v>
+        <v>0.2164</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>45202</v>
+        <v>45848</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>45204</v>
+        <v>45850</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>45207</v>
+        <v>45851</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>45207</v>
+        <v>45852</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>45207</v>
+        <v>45852</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>45214</v>
+        <v>45856</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>45215</v>
+        <v>45857</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>45215</v>
+        <v>45857</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>45220</v>
+        <v>45860</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>45221</v>
+        <v>45861</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>45223</v>
+        <v>45863</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>45230</v>
+        <v>45867</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8471,36 +8471,36 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PathoClear</t>
+          <t>LabReady Pro</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Gabriela Rocha</t>
+          <t>Fabio Lima</t>
         </is>
       </c>
       <c r="G168" t="n">
-        <v>7052.84</v>
+        <v>63500.26</v>
       </c>
       <c r="H168" t="n">
-        <v>7845.56</v>
+        <v>68060.81</v>
       </c>
       <c r="I168" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="J168" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="K168" t="n">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="L168" t="n">
-        <v>0.2167</v>
+        <v>0.1551</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>45230</v>
+        <v>45868</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8519,36 +8519,36 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>LabReady Pro</t>
+          <t>PathoClear</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fabio Lima</t>
+          <t>Gabriela Rocha</t>
         </is>
       </c>
       <c r="G169" t="n">
-        <v>63500.26</v>
+        <v>7052.84</v>
       </c>
       <c r="H169" t="n">
-        <v>68060.81</v>
+        <v>7845.56</v>
       </c>
       <c r="I169" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="J169" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K169" t="n">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="L169" t="n">
-        <v>0.1551</v>
+        <v>0.2167</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>45235</v>
+        <v>45871</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -8596,103 +8596,103 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>45236</v>
+        <v>45871</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>IV FlowMaster</t>
+          <t>OrthoFix Plus</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>João Mendes</t>
+          <t>Bruno Martins</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>13087.75</v>
+        <v>66368.3</v>
       </c>
       <c r="H171" t="n">
-        <v>11989.02</v>
+        <v>62393.38</v>
       </c>
       <c r="I171" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J171" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K171" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="L171" t="n">
-        <v>0.1116</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>45236</v>
+        <v>45872</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>OrthoFix Plus</t>
+          <t>IV FlowMaster</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bruno Martins</t>
+          <t>João Mendes</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>66368.3</v>
+        <v>13087.75</v>
       </c>
       <c r="H172" t="n">
-        <v>62393.38</v>
+        <v>11989.02</v>
       </c>
       <c r="I172" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J172" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K172" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L172" t="n">
-        <v>0.126</v>
+        <v>0.1116</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>45237</v>
+        <v>45872</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>45241</v>
+        <v>45875</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>45243</v>
+        <v>45876</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>45244</v>
+        <v>45877</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -8845,242 +8845,242 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>MedScan 200</t>
+          <t>ClinAssay 500</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Alice Santos</t>
+          <t>Isabela Ferreira</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>33795.43</v>
+        <v>47685.23</v>
       </c>
       <c r="H176" t="n">
-        <v>35071.91</v>
+        <v>45344.59</v>
       </c>
       <c r="I176" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J176" t="n">
         <v>10</v>
       </c>
       <c r="K176" t="n">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="L176" t="n">
-        <v>0.2409</v>
+        <v>0.0349</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>45244</v>
+        <v>45877</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>HospCore Suite</t>
+          <t>MedScan 200</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Elena Costa</t>
+          <t>Alice Santos</t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>76599.69</v>
+        <v>33795.43</v>
       </c>
       <c r="H177" t="n">
-        <v>82328.45</v>
+        <v>35071.91</v>
       </c>
       <c r="I177" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="J177" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K177" t="n">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="L177" t="n">
-        <v>0.2457</v>
+        <v>0.2409</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>45244</v>
+        <v>45877</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>ClinAssay 500</t>
+          <t>HospCore Suite</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Isabela Ferreira</t>
+          <t>Elena Costa</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>47685.23</v>
+        <v>76599.69</v>
       </c>
       <c r="H178" t="n">
-        <v>45344.59</v>
+        <v>82328.45</v>
       </c>
       <c r="I178" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="J178" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K178" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L178" t="n">
-        <v>0.0349</v>
+        <v>0.2457</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>45246</v>
+        <v>45879</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Consumer Health Simulation</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>MedScan 200</t>
+          <t>CareSimPack</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gabriela Rocha</t>
+          <t>Carla Oliveira</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>32976.3</v>
+        <v>32279.07</v>
       </c>
       <c r="H179" t="n">
-        <v>33297.53</v>
+        <v>31513.53</v>
       </c>
       <c r="I179" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J179" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="K179" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="L179" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.1169</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>45247</v>
+        <v>45879</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Consumer Health Simulation</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>CareSimPack</t>
+          <t>MedScan 200</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Carla Oliveira</t>
+          <t>Gabriela Rocha</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>32279.07</v>
+        <v>32976.3</v>
       </c>
       <c r="H180" t="n">
-        <v>31513.53</v>
+        <v>33297.53</v>
       </c>
       <c r="I180" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J180" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="K180" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="L180" t="n">
-        <v>0.1169</v>
+        <v>0.09039999999999999</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>45247</v>
+        <v>45880</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -9090,45 +9090,45 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Consumer Health Simulation</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>WellnessSet Pro</t>
+          <t>MedScan 200</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Fabio Lima</t>
+          <t>Bruno Martins</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>32265.77</v>
+        <v>46764.98</v>
       </c>
       <c r="H181" t="n">
-        <v>33809.13</v>
+        <v>47073.04</v>
       </c>
       <c r="I181" t="n">
+        <v>28</v>
+      </c>
+      <c r="J181" t="n">
+        <v>20</v>
+      </c>
+      <c r="K181" t="n">
         <v>35</v>
       </c>
-      <c r="J181" t="n">
-        <v>3</v>
-      </c>
-      <c r="K181" t="n">
-        <v>76</v>
-      </c>
       <c r="L181" t="n">
-        <v>0.1587</v>
+        <v>0.1169</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>45248</v>
+        <v>45880</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -9138,41 +9138,41 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Consumer Health Simulation</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>MedScan 200</t>
+          <t>WellnessSet Pro</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Bruno Martins</t>
+          <t>Fabio Lima</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>46764.98</v>
+        <v>32265.77</v>
       </c>
       <c r="H182" t="n">
-        <v>47073.04</v>
+        <v>33809.13</v>
       </c>
       <c r="I182" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J182" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K182" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="L182" t="n">
-        <v>0.1169</v>
+        <v>0.1587</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>45250</v>
+        <v>45881</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>45252</v>
+        <v>45882</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>45255</v>
+        <v>45885</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -9316,16 +9316,16 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>45255</v>
+        <v>45885</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9335,45 +9335,45 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>MobilityAid Plus</t>
+          <t>RecoverEase</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Henrique Silva</t>
+          <t>Fabio Lima</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>65557.37</v>
+        <v>77790.5</v>
       </c>
       <c r="H186" t="n">
-        <v>78640.00999999999</v>
+        <v>75371.81</v>
       </c>
       <c r="I186" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="J186" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="K186" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="L186" t="n">
-        <v>0.102</v>
+        <v>0.1188</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>45256</v>
+        <v>45885</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9383,36 +9383,36 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>RecoverEase</t>
+          <t>MobilityAid Plus</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Fabio Lima</t>
+          <t>Henrique Silva</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>77790.5</v>
+        <v>65557.37</v>
       </c>
       <c r="H187" t="n">
-        <v>75371.81</v>
+        <v>78640.00999999999</v>
       </c>
       <c r="I187" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="J187" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="K187" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="L187" t="n">
-        <v>0.1188</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>45258</v>
+        <v>45887</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>45259</v>
+        <v>45888</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -9469,46 +9469,46 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>HospCore Suite</t>
+          <t>MedScan 200</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Fabio Lima</t>
         </is>
       </c>
       <c r="G189" t="n">
-        <v>69217.17999999999</v>
+        <v>11495.42</v>
       </c>
       <c r="H189" t="n">
-        <v>74122.8</v>
+        <v>11801.04</v>
       </c>
       <c r="I189" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="J189" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K189" t="n">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="L189" t="n">
-        <v>0.1656</v>
+        <v>0.1575</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>45260</v>
+        <v>45888</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -9517,142 +9517,142 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>MedScan 200</t>
+          <t>HospCore Suite</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Fabio Lima</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>11495.42</v>
+        <v>69217.17999999999</v>
       </c>
       <c r="H190" t="n">
-        <v>11801.04</v>
+        <v>74122.8</v>
       </c>
       <c r="I190" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="J190" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K190" t="n">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="L190" t="n">
-        <v>0.1575</v>
+        <v>0.1656</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>45265</v>
+        <v>45891</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>HospCore Suite</t>
+          <t>PathoClear</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Henrique Silva</t>
+          <t>Isabela Ferreira</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>86844.28</v>
+        <v>49511.17</v>
       </c>
       <c r="H191" t="n">
-        <v>88181.21000000001</v>
+        <v>54552</v>
       </c>
       <c r="I191" t="n">
+        <v>43</v>
+      </c>
+      <c r="J191" t="n">
         <v>29</v>
       </c>
-      <c r="J191" t="n">
-        <v>16</v>
-      </c>
       <c r="K191" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="L191" t="n">
-        <v>0.1549</v>
+        <v>0.1568</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>45265</v>
+        <v>45892</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>PathoClear</t>
+          <t>HospCore Suite</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Isabela Ferreira</t>
+          <t>Henrique Silva</t>
         </is>
       </c>
       <c r="G192" t="n">
-        <v>49511.17</v>
+        <v>86844.28</v>
       </c>
       <c r="H192" t="n">
-        <v>54552</v>
+        <v>88181.21000000001</v>
       </c>
       <c r="I192" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="J192" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="K192" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="L192" t="n">
-        <v>0.1568</v>
+        <v>0.1549</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>45270</v>
+        <v>45895</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>45273</v>
+        <v>45897</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>45274</v>
+        <v>45898</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>45275</v>
+        <v>45899</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>45277</v>
+        <v>45900</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>45282</v>
+        <v>45904</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>45284</v>
+        <v>45905</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>45286</v>
+        <v>45906</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>45289</v>
+        <v>45908</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>45292</v>
+        <v>45910</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>45294</v>
+        <v>45911</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>45296</v>
+        <v>45913</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -10228,11 +10228,11 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>45297</v>
+        <v>45914</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>MedScan 200</t>
+          <t>IV FlowMaster</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -10256,27 +10256,27 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>33381.98</v>
+        <v>61505.75</v>
       </c>
       <c r="H205" t="n">
-        <v>39889.43</v>
+        <v>73709.25999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J205" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K205" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="L205" t="n">
-        <v>0.2445</v>
+        <v>0.07770000000000001</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>45297</v>
+        <v>45914</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -10324,11 +10324,11 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>45298</v>
+        <v>45914</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>IV FlowMaster</t>
+          <t>MedScan 200</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -10352,27 +10352,27 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>61505.75</v>
+        <v>33381.98</v>
       </c>
       <c r="H207" t="n">
-        <v>73709.25999999999</v>
+        <v>39889.43</v>
       </c>
       <c r="I207" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="J207" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="K207" t="n">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="L207" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.2445</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>45301</v>
+        <v>45917</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>45301</v>
+        <v>45917</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>45304</v>
+        <v>45918</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>45305</v>
+        <v>45919</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>45306</v>
+        <v>45920</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>45309</v>
+        <v>45922</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>45311</v>
+        <v>45923</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -10708,26 +10708,26 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>45313</v>
+        <v>45925</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Patient Care</t>
+          <t>Consumer Health Simulation</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>NutriSupport Kit</t>
+          <t>HealthTrack Kit</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -10736,46 +10736,46 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>40861.5</v>
+        <v>50116.88</v>
       </c>
       <c r="H215" t="n">
-        <v>38200.15</v>
+        <v>51127.6</v>
       </c>
       <c r="I215" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J215" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K215" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="L215" t="n">
-        <v>0.1708</v>
+        <v>0.1047</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>45314</v>
+        <v>45925</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Consumer Health Simulation</t>
+          <t>Patient Care</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>HealthTrack Kit</t>
+          <t>NutriSupport Kit</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -10784,27 +10784,27 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>50116.88</v>
+        <v>40861.5</v>
       </c>
       <c r="H216" t="n">
-        <v>51127.6</v>
+        <v>38200.15</v>
       </c>
       <c r="I216" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J216" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K216" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="L216" t="n">
-        <v>0.1047</v>
+        <v>0.1708</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>45314</v>
+        <v>45926</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>45316</v>
+        <v>45927</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>45316</v>
+        <v>45927</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -10948,11 +10948,11 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>45317</v>
+        <v>45928</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -10962,45 +10962,45 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>PathoClear</t>
+          <t>MedScan 200</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Fabio Lima</t>
+          <t>Gabriela Rocha</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>23630.48</v>
+        <v>18612.38</v>
       </c>
       <c r="H220" t="n">
-        <v>22110.54</v>
+        <v>17362.76</v>
       </c>
       <c r="I220" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="J220" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K220" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L220" t="n">
-        <v>0.235</v>
+        <v>0.1428</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>45318</v>
+        <v>45928</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -11010,41 +11010,41 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>MedScan 200</t>
+          <t>PathoClear</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Gabriela Rocha</t>
+          <t>Fabio Lima</t>
         </is>
       </c>
       <c r="G221" t="n">
-        <v>18612.38</v>
+        <v>23630.48</v>
       </c>
       <c r="H221" t="n">
-        <v>17362.76</v>
+        <v>22110.54</v>
       </c>
       <c r="I221" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="J221" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K221" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="L221" t="n">
-        <v>0.1428</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>45319</v>
+        <v>45929</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>45320</v>
+        <v>45930</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>45320</v>
+        <v>45930</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -11188,16 +11188,16 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>45321</v>
+        <v>45931</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -11207,45 +11207,45 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>HealthTrack Kit</t>
+          <t>VitaBalance</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Gabriela Rocha</t>
+          <t>João Mendes</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>62553.85</v>
+        <v>51418.73</v>
       </c>
       <c r="H225" t="n">
-        <v>71608.78</v>
+        <v>57382.71</v>
       </c>
       <c r="I225" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="J225" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K225" t="n">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="L225" t="n">
-        <v>0.0317</v>
+        <v>0.1952</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>45322</v>
+        <v>45931</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -11255,36 +11255,36 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>VitaBalance</t>
+          <t>HealthTrack Kit</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>João Mendes</t>
+          <t>Gabriela Rocha</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>51418.73</v>
+        <v>62553.85</v>
       </c>
       <c r="H226" t="n">
-        <v>57382.71</v>
+        <v>71608.78</v>
       </c>
       <c r="I226" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="J226" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K226" t="n">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="L226" t="n">
-        <v>0.1952</v>
+        <v>0.0317</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>45323</v>
+        <v>45932</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>45324</v>
+        <v>45933</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>45326</v>
+        <v>45934</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>45332</v>
+        <v>45938</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>45333</v>
+        <v>45939</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>45335</v>
+        <v>45940</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>45339</v>
+        <v>45943</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>45341</v>
+        <v>45944</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>45345</v>
+        <v>45947</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>45348</v>
+        <v>45949</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>45351</v>
+        <v>45951</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>45352</v>
+        <v>45952</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>45353</v>
+        <v>45953</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>45357</v>
+        <v>45955</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>45363</v>
+        <v>45960</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>45370</v>
+        <v>45965</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>45373</v>
+        <v>45966</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>45375</v>
+        <v>45968</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>45376</v>
+        <v>45969</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>45379</v>
+        <v>45970</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>45382</v>
+        <v>45972</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>45382</v>
+        <v>45972</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>45384</v>
+        <v>45974</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>45386</v>
+        <v>45975</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>45386</v>
+        <v>45975</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>45388</v>
+        <v>45977</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>45388</v>
+        <v>45977</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
-        <v>45390</v>
+        <v>45978</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>45391</v>
+        <v>45979</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>45393</v>
+        <v>45980</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>45400</v>
+        <v>45985</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>45401</v>
+        <v>45986</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>45402</v>
+        <v>45987</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>45402</v>
+        <v>45987</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>45404</v>
+        <v>45988</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>45407</v>
+        <v>45990</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>45409</v>
+        <v>45991</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>45413</v>
+        <v>45994</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>45416</v>
+        <v>45996</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>45419</v>
+        <v>45998</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>45422</v>
+        <v>46001</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>45426</v>
+        <v>46003</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>45431</v>
+        <v>46006</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>45437</v>
+        <v>46011</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>45437</v>
+        <v>46011</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -13444,103 +13444,103 @@
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>45437</v>
+        <v>46011</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>MedScan 200</t>
+          <t>BedCare System</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Henrique Silva</t>
+          <t>João Mendes</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>50547.47</v>
+        <v>45690.35</v>
       </c>
       <c r="H272" t="n">
-        <v>56620.61</v>
+        <v>45936.16</v>
       </c>
       <c r="I272" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="J272" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K272" t="n">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="L272" t="n">
-        <v>0.2088</v>
+        <v>0.2135</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>45437</v>
+        <v>46011</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Consumer Health Simulation</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>WellnessSet Pro</t>
+          <t>MedScan 200</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Isabela Ferreira</t>
+          <t>Henrique Silva</t>
         </is>
       </c>
       <c r="G273" t="n">
-        <v>13055.22</v>
+        <v>50547.47</v>
       </c>
       <c r="H273" t="n">
-        <v>11623.9</v>
+        <v>56620.61</v>
       </c>
       <c r="I273" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J273" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K273" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L273" t="n">
-        <v>0.0305</v>
+        <v>0.2088</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>45438</v>
+        <v>46011</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -13549,46 +13549,46 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Consumer Health Simulation</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>BedCare System</t>
+          <t>WellnessSet Pro</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>João Mendes</t>
+          <t>Isabela Ferreira</t>
         </is>
       </c>
       <c r="G274" t="n">
-        <v>45690.35</v>
+        <v>13055.22</v>
       </c>
       <c r="H274" t="n">
-        <v>45936.16</v>
+        <v>11623.9</v>
       </c>
       <c r="I274" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="J274" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K274" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="L274" t="n">
-        <v>0.2135</v>
+        <v>0.0305</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>45442</v>
+        <v>46014</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -13636,11 +13636,11 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>45444</v>
+        <v>46015</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -13650,12 +13650,12 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Patient Care</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>MobilityAid Plus</t>
+          <t>OrthoFix Plus</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -13664,31 +13664,31 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>25337.35</v>
+        <v>83626.98</v>
       </c>
       <c r="H276" t="n">
-        <v>22010.14</v>
+        <v>95932.06</v>
       </c>
       <c r="I276" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J276" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K276" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="L276" t="n">
-        <v>0.1702</v>
+        <v>0.1275</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>45444</v>
+        <v>46016</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -13698,12 +13698,12 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Patient Care</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>OrthoFix Plus</t>
+          <t>MobilityAid Plus</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -13712,27 +13712,27 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>83626.98</v>
+        <v>25337.35</v>
       </c>
       <c r="H277" t="n">
-        <v>95932.06</v>
+        <v>22010.14</v>
       </c>
       <c r="I277" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J277" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K277" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="L277" t="n">
-        <v>0.1275</v>
+        <v>0.1702</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>45444</v>
+        <v>46016</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>45447</v>
+        <v>46018</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>45449</v>
+        <v>46019</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>45450</v>
+        <v>46020</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>45451</v>
+        <v>46020</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>45453</v>
+        <v>46022</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>45453</v>
+        <v>46022</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>45453</v>
+        <v>46022</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -14116,107 +14116,107 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>45455</v>
+        <v>46023</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Consumer Health Simulation</t>
+          <t>Patient Care</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>WellnessSet Pro</t>
+          <t>MobilityAid Plus</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Elena Costa</t>
         </is>
       </c>
       <c r="G286" t="n">
-        <v>40076.93</v>
+        <v>69224.42</v>
       </c>
       <c r="H286" t="n">
-        <v>47618.65</v>
+        <v>78245.02</v>
       </c>
       <c r="I286" t="n">
         <v>11</v>
       </c>
       <c r="J286" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K286" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L286" t="n">
-        <v>0.2333</v>
+        <v>0.1957</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>45455</v>
+        <v>46023</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Patient Care</t>
+          <t>Consumer Health Simulation</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>MobilityAid Plus</t>
+          <t>WellnessSet Pro</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Elena Costa</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="G287" t="n">
-        <v>69224.42</v>
+        <v>40076.93</v>
       </c>
       <c r="H287" t="n">
-        <v>78245.02</v>
+        <v>47618.65</v>
       </c>
       <c r="I287" t="n">
         <v>11</v>
       </c>
       <c r="J287" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K287" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L287" t="n">
-        <v>0.1957</v>
+        <v>0.2333</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>45459</v>
+        <v>46026</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -14226,45 +14226,45 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Patient Care</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>ComfortBrace</t>
+          <t>WoundShield</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Alice Santos</t>
+          <t>Carla Oliveira</t>
         </is>
       </c>
       <c r="G288" t="n">
-        <v>36873.45</v>
+        <v>63074.11</v>
       </c>
       <c r="H288" t="n">
-        <v>36117.34</v>
+        <v>68431.06</v>
       </c>
       <c r="I288" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J288" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="K288" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="L288" t="n">
-        <v>0.0296</v>
+        <v>0.2246</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>45459</v>
+        <v>46026</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -14274,41 +14274,41 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Patient Care</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>WoundShield</t>
+          <t>ComfortBrace</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Carla Oliveira</t>
+          <t>Alice Santos</t>
         </is>
       </c>
       <c r="G289" t="n">
-        <v>63074.11</v>
+        <v>36873.45</v>
       </c>
       <c r="H289" t="n">
-        <v>68431.06</v>
+        <v>36117.34</v>
       </c>
       <c r="I289" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J289" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="K289" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="L289" t="n">
-        <v>0.2246</v>
+        <v>0.0296</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>45461</v>
+        <v>46027</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>45462</v>
+        <v>46028</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>45463</v>
+        <v>46029</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -14452,16 +14452,16 @@
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>45464</v>
+        <v>46029</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -14476,31 +14476,31 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Elena Costa</t>
+          <t>Bruno Martins</t>
         </is>
       </c>
       <c r="G293" t="n">
-        <v>46843.73</v>
+        <v>7070.32</v>
       </c>
       <c r="H293" t="n">
-        <v>51060.14</v>
+        <v>6419.29</v>
       </c>
       <c r="I293" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J293" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K293" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="L293" t="n">
-        <v>0.2372</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>45464</v>
+        <v>46030</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -14509,94 +14509,94 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Patient Care</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>IV FlowMaster</t>
+          <t>ComfortBrace</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Bruno Martins</t>
+          <t>Alice Santos</t>
         </is>
       </c>
       <c r="G294" t="n">
-        <v>7070.32</v>
+        <v>32042.9</v>
       </c>
       <c r="H294" t="n">
-        <v>6419.29</v>
+        <v>36037.6</v>
       </c>
       <c r="I294" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J294" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="K294" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="L294" t="n">
-        <v>0.177</v>
+        <v>0.0273</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>45465</v>
+        <v>46030</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Patient Care</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>ComfortBrace</t>
+          <t>IV FlowMaster</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Alice Santos</t>
+          <t>Elena Costa</t>
         </is>
       </c>
       <c r="G295" t="n">
-        <v>32042.9</v>
+        <v>46843.73</v>
       </c>
       <c r="H295" t="n">
-        <v>36037.6</v>
+        <v>51060.14</v>
       </c>
       <c r="I295" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="J295" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="K295" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="L295" t="n">
-        <v>0.0273</v>
+        <v>0.2372</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>45467</v>
+        <v>46031</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>45467</v>
+        <v>46031</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>45472</v>
+        <v>46035</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>45477</v>
+        <v>46039</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>45481</v>
+        <v>46041</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>45481</v>
+        <v>46041</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>45484</v>
+        <v>46043</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>45484</v>
+        <v>46043</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>45488</v>
+        <v>46046</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
@@ -15028,16 +15028,16 @@
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
-        <v>45489</v>
+        <v>46046</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -15052,40 +15052,40 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Fabio Lima</t>
+          <t>Gabriela Rocha</t>
         </is>
       </c>
       <c r="G305" t="n">
-        <v>52114.93</v>
+        <v>62801.63</v>
       </c>
       <c r="H305" t="n">
-        <v>51372.01</v>
+        <v>63460.81</v>
       </c>
       <c r="I305" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="J305" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="K305" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="L305" t="n">
-        <v>0.0027</v>
+        <v>0.1591</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
-        <v>45489</v>
+        <v>46047</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -15100,31 +15100,31 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Gabriela Rocha</t>
+          <t>Fabio Lima</t>
         </is>
       </c>
       <c r="G306" t="n">
-        <v>62801.63</v>
+        <v>52114.93</v>
       </c>
       <c r="H306" t="n">
-        <v>63460.81</v>
+        <v>51372.01</v>
       </c>
       <c r="I306" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="J306" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="K306" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="L306" t="n">
-        <v>0.1591</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
-        <v>45490</v>
+        <v>46047</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
@@ -15172,11 +15172,11 @@
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
-        <v>45493</v>
+        <v>46050</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -15186,45 +15186,45 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Patient Care</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>PathoClear</t>
+          <t>RecoverEase</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Elena Costa</t>
+          <t>Fabio Lima</t>
         </is>
       </c>
       <c r="G308" t="n">
-        <v>45585.73</v>
+        <v>61635.22</v>
       </c>
       <c r="H308" t="n">
-        <v>41507.19</v>
+        <v>60391.38</v>
       </c>
       <c r="I308" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="J308" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K308" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L308" t="n">
-        <v>0.2479</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
-        <v>45494</v>
+        <v>46050</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -15234,50 +15234,50 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Patient Care</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>RecoverEase</t>
+          <t>PathoClear</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Fabio Lima</t>
+          <t>Elena Costa</t>
         </is>
       </c>
       <c r="G309" t="n">
-        <v>61635.22</v>
+        <v>45585.73</v>
       </c>
       <c r="H309" t="n">
-        <v>60391.38</v>
+        <v>41507.19</v>
       </c>
       <c r="I309" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="J309" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K309" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="L309" t="n">
-        <v>0.203</v>
+        <v>0.2479</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
-        <v>45495</v>
+        <v>46051</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -15292,40 +15292,40 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Fabio Lima</t>
+          <t>Elena Costa</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>55934.35</v>
+        <v>33725.64</v>
       </c>
       <c r="H310" t="n">
-        <v>63168.57</v>
+        <v>29089.88</v>
       </c>
       <c r="I310" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="J310" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K310" t="n">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="L310" t="n">
-        <v>0.0511</v>
+        <v>0.0258</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
-        <v>45496</v>
+        <v>46051</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -15340,83 +15340,83 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Elena Costa</t>
+          <t>Fabio Lima</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>33725.64</v>
+        <v>55934.35</v>
       </c>
       <c r="H311" t="n">
-        <v>29089.88</v>
+        <v>63168.57</v>
       </c>
       <c r="I311" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="J311" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K311" t="n">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="L311" t="n">
-        <v>0.0258</v>
+        <v>0.0511</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
-        <v>45503</v>
+        <v>46057</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Patient Care</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>RecoverEase</t>
+          <t>WoundShield</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Gabriela Rocha</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>12350.85</v>
+        <v>19070.7</v>
       </c>
       <c r="H312" t="n">
-        <v>10980.65</v>
+        <v>20176.71</v>
       </c>
       <c r="I312" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J312" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="K312" t="n">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="L312" t="n">
-        <v>0.0151</v>
+        <v>0.0936</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
-        <v>45505</v>
+        <v>46057</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -15426,89 +15426,89 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Patient Care</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>ClinAssay 500</t>
+          <t>RecoverEase</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Henrique Silva</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>13627.3</v>
+        <v>12350.85</v>
       </c>
       <c r="H313" t="n">
-        <v>16203.72</v>
+        <v>10980.65</v>
       </c>
       <c r="I313" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J313" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K313" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L313" t="n">
-        <v>0.0473</v>
+        <v>0.0151</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
-        <v>45505</v>
+        <v>46058</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>WoundShield</t>
+          <t>ClinAssay 500</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Gabriela Rocha</t>
+          <t>Henrique Silva</t>
         </is>
       </c>
       <c r="G314" t="n">
-        <v>19070.7</v>
+        <v>13627.3</v>
       </c>
       <c r="H314" t="n">
-        <v>20176.71</v>
+        <v>16203.72</v>
       </c>
       <c r="I314" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="J314" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="K314" t="n">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="L314" t="n">
-        <v>0.0936</v>
+        <v>0.0473</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
-        <v>45506</v>
+        <v>46058</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
     </row>
     <row r="316">
       <c r="A316" s="1" t="n">
-        <v>45507</v>
+        <v>46059</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -15604,103 +15604,103 @@
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
-        <v>45510</v>
+        <v>46061</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>WoundShield</t>
+          <t>OrthoFix Plus</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Fabio Lima</t>
+          <t>Bruno Martins</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>29765.1</v>
+        <v>20075.38</v>
       </c>
       <c r="H317" t="n">
-        <v>32447.46</v>
+        <v>17255.07</v>
       </c>
       <c r="I317" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="J317" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="K317" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L317" t="n">
-        <v>0.0194</v>
+        <v>0.1775</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
-        <v>45510</v>
+        <v>46061</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>OrthoFix Plus</t>
+          <t>WoundShield</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Bruno Martins</t>
+          <t>Fabio Lima</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>20075.38</v>
+        <v>29765.1</v>
       </c>
       <c r="H318" t="n">
-        <v>17255.07</v>
+        <v>32447.46</v>
       </c>
       <c r="I318" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="J318" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="K318" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="L318" t="n">
-        <v>0.1775</v>
+        <v>0.0194</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
-        <v>45511</v>
+        <v>46062</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
-        <v>45512</v>
+        <v>46063</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
-        <v>45513</v>
+        <v>46063</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
-        <v>45516</v>
+        <v>46065</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
-        <v>45517</v>
+        <v>46066</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
-        <v>45517</v>
+        <v>46066</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
-        <v>45521</v>
+        <v>46069</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
-        <v>45523</v>
+        <v>46070</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
-        <v>45526</v>
+        <v>46072</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
@@ -16132,26 +16132,26 @@
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
-        <v>45529</v>
+        <v>46075</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>FlexCath Pro</t>
+          <t>LabReady Pro</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -16160,46 +16160,46 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>14148.08</v>
+        <v>77086.44</v>
       </c>
       <c r="H328" t="n">
-        <v>13074.53</v>
+        <v>83209.50999999999</v>
       </c>
       <c r="I328" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J328" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K328" t="n">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="L328" t="n">
-        <v>0.03</v>
+        <v>0.0049</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
-        <v>45530</v>
+        <v>46075</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>LabReady Pro</t>
+          <t>FlexCath Pro</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -16208,27 +16208,27 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>77086.44</v>
+        <v>14148.08</v>
       </c>
       <c r="H329" t="n">
-        <v>83209.50999999999</v>
+        <v>13074.53</v>
       </c>
       <c r="I329" t="n">
+        <v>19</v>
+      </c>
+      <c r="J329" t="n">
+        <v>3</v>
+      </c>
+      <c r="K329" t="n">
         <v>9</v>
       </c>
-      <c r="J329" t="n">
-        <v>7</v>
-      </c>
-      <c r="K329" t="n">
-        <v>66</v>
-      </c>
       <c r="L329" t="n">
-        <v>0.0049</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
-        <v>45531</v>
+        <v>46076</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
-        <v>45534</v>
+        <v>46078</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
-        <v>45534</v>
+        <v>46078</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
-        <v>45535</v>
+        <v>46079</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
-        <v>45537</v>
+        <v>46080</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
@@ -16468,16 +16468,16 @@
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
-        <v>45539</v>
+        <v>46082</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -16487,228 +16487,228 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>OrthoFix Plus</t>
+          <t>FlexCath Pro</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Elena Costa</t>
+          <t>Henrique Silva</t>
         </is>
       </c>
       <c r="G335" t="n">
-        <v>73010.39999999999</v>
+        <v>40246.7</v>
       </c>
       <c r="H335" t="n">
-        <v>81009.78999999999</v>
+        <v>40916.09</v>
       </c>
       <c r="I335" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J335" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="K335" t="n">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="L335" t="n">
-        <v>0.0382</v>
+        <v>0.0149</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
-        <v>45540</v>
+        <v>46082</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>FlexCath Pro</t>
+          <t>ClinAssay 500</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Henrique Silva</t>
+          <t>Gabriela Rocha</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>40246.7</v>
+        <v>7452.11</v>
       </c>
       <c r="H336" t="n">
-        <v>40916.09</v>
+        <v>7824.03</v>
       </c>
       <c r="I336" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="J336" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="K336" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="L336" t="n">
-        <v>0.0149</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
-        <v>45540</v>
+        <v>46082</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>ClinAssay 500</t>
+          <t>OrthoFix Plus</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Gabriela Rocha</t>
+          <t>Elena Costa</t>
         </is>
       </c>
       <c r="G337" t="n">
-        <v>7452.11</v>
+        <v>73010.39999999999</v>
       </c>
       <c r="H337" t="n">
-        <v>7824.03</v>
+        <v>81009.78999999999</v>
       </c>
       <c r="I337" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="J337" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="K337" t="n">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="L337" t="n">
-        <v>0.0097</v>
+        <v>0.0382</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
-        <v>45544</v>
+        <v>46085</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>FlexCath Pro</t>
+          <t>WoundShield</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Alice Santos</t>
+          <t>Isabela Ferreira</t>
         </is>
       </c>
       <c r="G338" t="n">
-        <v>79209.35000000001</v>
+        <v>74292.53</v>
       </c>
       <c r="H338" t="n">
-        <v>81712.39999999999</v>
+        <v>78203.45</v>
       </c>
       <c r="I338" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="J338" t="n">
         <v>22</v>
       </c>
       <c r="K338" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="L338" t="n">
-        <v>0.193</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
-        <v>45545</v>
+        <v>46085</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>WoundShield</t>
+          <t>FlexCath Pro</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Isabela Ferreira</t>
+          <t>Alice Santos</t>
         </is>
       </c>
       <c r="G339" t="n">
-        <v>74292.53</v>
+        <v>79209.35000000001</v>
       </c>
       <c r="H339" t="n">
-        <v>78203.45</v>
+        <v>81712.39999999999</v>
       </c>
       <c r="I339" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J339" t="n">
         <v>22</v>
       </c>
       <c r="K339" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="L339" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
-        <v>45550</v>
+        <v>46089</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
-        <v>45551</v>
+        <v>46090</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
@@ -16804,103 +16804,103 @@
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
-        <v>45557</v>
+        <v>46093</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Consumer Health Simulation</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>VitaBalance</t>
+          <t>WoundShield</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Alice Santos</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="G342" t="n">
-        <v>13027.24</v>
+        <v>51920.47</v>
       </c>
       <c r="H342" t="n">
-        <v>11289.16</v>
+        <v>57862.19</v>
       </c>
       <c r="I342" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="J342" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K342" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="L342" t="n">
-        <v>0.2297</v>
+        <v>0.2067</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
-        <v>45557</v>
+        <v>46094</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Consumer Health Simulation</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>WoundShield</t>
+          <t>VitaBalance</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Alice Santos</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>51920.47</v>
+        <v>13027.24</v>
       </c>
       <c r="H343" t="n">
-        <v>57862.19</v>
+        <v>11289.16</v>
       </c>
       <c r="I343" t="n">
+        <v>37</v>
+      </c>
+      <c r="J343" t="n">
+        <v>12</v>
+      </c>
+      <c r="K343" t="n">
         <v>14</v>
       </c>
-      <c r="J343" t="n">
-        <v>8</v>
-      </c>
-      <c r="K343" t="n">
-        <v>26</v>
-      </c>
       <c r="L343" t="n">
-        <v>0.2067</v>
+        <v>0.2297</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
-        <v>45558</v>
+        <v>46094</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
-        <v>45563</v>
+        <v>46097</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
-        <v>45564</v>
+        <v>46098</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
@@ -17044,26 +17044,26 @@
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
-        <v>45567</v>
+        <v>46101</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Consumer Health Simulation</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>VitaBalance</t>
+          <t>ClinAssay 500</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -17072,36 +17072,36 @@
         </is>
       </c>
       <c r="G347" t="n">
-        <v>15558.54</v>
+        <v>55117.51</v>
       </c>
       <c r="H347" t="n">
-        <v>16428.11</v>
+        <v>49339.02</v>
       </c>
       <c r="I347" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="J347" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K347" t="n">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="L347" t="n">
-        <v>0.0031</v>
+        <v>0.1581</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
-        <v>45568</v>
+        <v>46101</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>ClinAssay 500</t>
+          <t>LabReady Pro</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -17120,27 +17120,27 @@
         </is>
       </c>
       <c r="G348" t="n">
-        <v>55117.51</v>
+        <v>55896.7</v>
       </c>
       <c r="H348" t="n">
-        <v>49339.02</v>
+        <v>65184.76</v>
       </c>
       <c r="I348" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="J348" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K348" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="L348" t="n">
-        <v>0.1581</v>
+        <v>0.2408</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
-        <v>45568</v>
+        <v>46101</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
@@ -17149,17 +17149,17 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Consumer Health Simulation</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>LabReady Pro</t>
+          <t>VitaBalance</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -17168,79 +17168,79 @@
         </is>
       </c>
       <c r="G349" t="n">
-        <v>55896.7</v>
+        <v>15558.54</v>
       </c>
       <c r="H349" t="n">
-        <v>65184.76</v>
+        <v>16428.11</v>
       </c>
       <c r="I349" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="J349" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K349" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="L349" t="n">
-        <v>0.2408</v>
+        <v>0.0031</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
-        <v>45569</v>
+        <v>46102</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>WoundShield</t>
+          <t>ClinAssay 500</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Gabriela Rocha</t>
         </is>
       </c>
       <c r="G350" t="n">
-        <v>32875.77</v>
+        <v>54668.73</v>
       </c>
       <c r="H350" t="n">
-        <v>38981.56</v>
+        <v>55701.99</v>
       </c>
       <c r="I350" t="n">
         <v>20</v>
       </c>
       <c r="J350" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K350" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L350" t="n">
-        <v>0.1352</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
-        <v>45569</v>
+        <v>46102</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -17250,41 +17250,41 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>MedScan 200</t>
+          <t>WoundShield</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Carla Oliveira</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="G351" t="n">
-        <v>29681.59</v>
+        <v>32875.77</v>
       </c>
       <c r="H351" t="n">
-        <v>31099.7</v>
+        <v>38981.56</v>
       </c>
       <c r="I351" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="J351" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K351" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="L351" t="n">
-        <v>0.0401</v>
+        <v>0.1352</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
-        <v>45570</v>
+        <v>46102</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
@@ -17293,46 +17293,46 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>ClinAssay 500</t>
+          <t>MedScan 200</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Gabriela Rocha</t>
+          <t>Carla Oliveira</t>
         </is>
       </c>
       <c r="G352" t="n">
-        <v>54668.73</v>
+        <v>29681.59</v>
       </c>
       <c r="H352" t="n">
-        <v>55701.99</v>
+        <v>31099.7</v>
       </c>
       <c r="I352" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="J352" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K352" t="n">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="L352" t="n">
-        <v>0.213</v>
+        <v>0.0401</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
-        <v>45570</v>
+        <v>46103</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
-        <v>45570</v>
+        <v>46103</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
-        <v>45574</v>
+        <v>46106</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
-        <v>45578</v>
+        <v>46108</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
-        <v>45579</v>
+        <v>46109</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
-        <v>45582</v>
+        <v>46111</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
-        <v>45582</v>
+        <v>46111</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
-        <v>45593</v>
+        <v>46119</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
-        <v>45595</v>
+        <v>46120</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
-        <v>45595</v>
+        <v>46120</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
-        <v>45598</v>
+        <v>46122</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
-        <v>45599</v>
+        <v>46123</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
-        <v>45599</v>
+        <v>46123</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
@@ -17917,98 +17917,98 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>SurgiPro X1</t>
+          <t>BedCare System</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Elena Costa</t>
+          <t>Fabio Lima</t>
         </is>
       </c>
       <c r="G365" t="n">
-        <v>15504.16</v>
+        <v>69806.91</v>
       </c>
       <c r="H365" t="n">
-        <v>16856.09</v>
+        <v>67296.58</v>
       </c>
       <c r="I365" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="J365" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K365" t="n">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="L365" t="n">
-        <v>0.0588</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
-        <v>45600</v>
+        <v>46123</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>WoundShield</t>
+          <t>SurgiPro X1</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Fabio Lima</t>
+          <t>Elena Costa</t>
         </is>
       </c>
       <c r="G366" t="n">
-        <v>41333.11</v>
+        <v>15504.16</v>
       </c>
       <c r="H366" t="n">
-        <v>42995.67</v>
+        <v>16856.09</v>
       </c>
       <c r="I366" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J366" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="K366" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="L366" t="n">
-        <v>0.243</v>
+        <v>0.0588</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
-        <v>45600</v>
+        <v>46124</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -18023,7 +18023,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>BedCare System</t>
+          <t>WoundShield</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -18032,27 +18032,27 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>69806.91</v>
+        <v>41333.11</v>
       </c>
       <c r="H367" t="n">
-        <v>67296.58</v>
+        <v>42995.67</v>
       </c>
       <c r="I367" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J367" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K367" t="n">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="L367" t="n">
-        <v>0.1174</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
-        <v>45600</v>
+        <v>46124</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
-        <v>45604</v>
+        <v>46126</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
-        <v>45606</v>
+        <v>46128</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
-        <v>45608</v>
+        <v>46129</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
-        <v>45610</v>
+        <v>46130</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
@@ -18292,59 +18292,59 @@
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
-        <v>45610</v>
+        <v>46131</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Patient Care</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>NutriSupport Kit</t>
+          <t>DiagnoKit Elite</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Bruno Martins</t>
+          <t>Elena Costa</t>
         </is>
       </c>
       <c r="G373" t="n">
-        <v>45117.36</v>
+        <v>45779.22</v>
       </c>
       <c r="H373" t="n">
-        <v>52810.35</v>
+        <v>46060.98</v>
       </c>
       <c r="I373" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J373" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K373" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L373" t="n">
-        <v>0.0993</v>
+        <v>0.07539999999999999</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
-        <v>45611</v>
+        <v>46131</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -18354,41 +18354,41 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Patient Care</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>PathoClear</t>
+          <t>NutriSupport Kit</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Elena Costa</t>
+          <t>Bruno Martins</t>
         </is>
       </c>
       <c r="G374" t="n">
-        <v>36294.02</v>
+        <v>45117.36</v>
       </c>
       <c r="H374" t="n">
-        <v>38113.97</v>
+        <v>52810.35</v>
       </c>
       <c r="I374" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J374" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K374" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="L374" t="n">
-        <v>0.1849</v>
+        <v>0.0993</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
-        <v>45611</v>
+        <v>46131</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -18407,7 +18407,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>DiagnoKit Elite</t>
+          <t>PathoClear</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -18416,27 +18416,27 @@
         </is>
       </c>
       <c r="G375" t="n">
-        <v>45779.22</v>
+        <v>36294.02</v>
       </c>
       <c r="H375" t="n">
-        <v>46060.98</v>
+        <v>38113.97</v>
       </c>
       <c r="I375" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="J375" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="K375" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="L375" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.1849</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
-        <v>45613</v>
+        <v>46132</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
-        <v>45615</v>
+        <v>46134</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
-        <v>45617</v>
+        <v>46135</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
@@ -18580,16 +18580,16 @@
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
-        <v>45618</v>
+        <v>46136</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -18599,141 +18599,141 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>OrthoFix Plus</t>
+          <t>MedScan 200</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Carla Oliveira</t>
+          <t>Elena Costa</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>46711.05</v>
+        <v>19360.66</v>
       </c>
       <c r="H379" t="n">
-        <v>53629.09</v>
+        <v>21280.68</v>
       </c>
       <c r="I379" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="J379" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="K379" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L379" t="n">
-        <v>0.1547</v>
+        <v>0.1239</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
-        <v>45619</v>
+        <v>46136</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Hospital Solutions</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>HospCore Suite</t>
+          <t>OrthoFix Plus</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>João Mendes</t>
+          <t>Carla Oliveira</t>
         </is>
       </c>
       <c r="G380" t="n">
-        <v>8694.059999999999</v>
+        <v>46711.05</v>
       </c>
       <c r="H380" t="n">
-        <v>8526.83</v>
+        <v>53629.09</v>
       </c>
       <c r="I380" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J380" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="K380" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="L380" t="n">
-        <v>0.0254</v>
+        <v>0.1547</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
-        <v>45619</v>
+        <v>46137</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Hospital Solutions</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>MedScan 200</t>
+          <t>IV FlowMaster</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Elena Costa</t>
+          <t>João Mendes</t>
         </is>
       </c>
       <c r="G381" t="n">
-        <v>19360.66</v>
+        <v>44475.85</v>
       </c>
       <c r="H381" t="n">
-        <v>21280.68</v>
+        <v>50485.58</v>
       </c>
       <c r="I381" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="J381" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="K381" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="L381" t="n">
-        <v>0.1239</v>
+        <v>0.1969</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
-        <v>45620</v>
+        <v>46137</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -18743,7 +18743,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>IV FlowMaster</t>
+          <t>HospCore Suite</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -18752,27 +18752,27 @@
         </is>
       </c>
       <c r="G382" t="n">
-        <v>44475.85</v>
+        <v>8694.059999999999</v>
       </c>
       <c r="H382" t="n">
-        <v>50485.58</v>
+        <v>8526.83</v>
       </c>
       <c r="I382" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="J382" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K382" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="L382" t="n">
-        <v>0.1969</v>
+        <v>0.0254</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
-        <v>45622</v>
+        <v>46139</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
@@ -18820,11 +18820,11 @@
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
-        <v>45628</v>
+        <v>46142</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -18834,89 +18834,89 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Patient Care</t>
+          <t>Consumer Health Simulation</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>MobilityAid Plus</t>
+          <t>WellnessSet Pro</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Carla Oliveira</t>
+          <t>Isabela Ferreira</t>
         </is>
       </c>
       <c r="G384" t="n">
-        <v>7550.91</v>
+        <v>85072.81</v>
       </c>
       <c r="H384" t="n">
-        <v>7885.56</v>
+        <v>80190.41</v>
       </c>
       <c r="I384" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="J384" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K384" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="L384" t="n">
-        <v>0.0265</v>
+        <v>0.1081</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
-        <v>45628</v>
+        <v>46142</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Patient Care</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>ClinAssay 500</t>
+          <t>MobilityAid Plus</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Elena Costa</t>
+          <t>Carla Oliveira</t>
         </is>
       </c>
       <c r="G385" t="n">
-        <v>18967.03</v>
+        <v>7550.91</v>
       </c>
       <c r="H385" t="n">
-        <v>17048.86</v>
+        <v>7885.56</v>
       </c>
       <c r="I385" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="J385" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="K385" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="L385" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0265</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
-        <v>45628</v>
+        <v>46143</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
-        <v>45628</v>
+        <v>46143</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
@@ -18973,46 +18973,46 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Consumer Health Simulation</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>WellnessSet Pro</t>
+          <t>ClinAssay 500</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Isabela Ferreira</t>
+          <t>Elena Costa</t>
         </is>
       </c>
       <c r="G387" t="n">
-        <v>85072.81</v>
+        <v>18967.03</v>
       </c>
       <c r="H387" t="n">
-        <v>80190.41</v>
+        <v>17048.86</v>
       </c>
       <c r="I387" t="n">
+        <v>28</v>
+      </c>
+      <c r="J387" t="n">
         <v>17</v>
       </c>
-      <c r="J387" t="n">
-        <v>1</v>
-      </c>
       <c r="K387" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="L387" t="n">
-        <v>0.1081</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
-        <v>45633</v>
+        <v>46146</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
@@ -19060,103 +19060,103 @@
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
-        <v>45635</v>
+        <v>46148</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Patient Care</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>NutriSupport Kit</t>
+          <t>DiagnoKit Elite</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Bruno Martins</t>
+          <t>Henrique Silva</t>
         </is>
       </c>
       <c r="G389" t="n">
-        <v>44824.13</v>
+        <v>15577.05</v>
       </c>
       <c r="H389" t="n">
-        <v>48595.26</v>
+        <v>18541.69</v>
       </c>
       <c r="I389" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="J389" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="K389" t="n">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="L389" t="n">
-        <v>0.2364</v>
+        <v>0.2305</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
-        <v>45636</v>
+        <v>46148</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Patient Care</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>DiagnoKit Elite</t>
+          <t>NutriSupport Kit</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Henrique Silva</t>
+          <t>Bruno Martins</t>
         </is>
       </c>
       <c r="G390" t="n">
-        <v>15577.05</v>
+        <v>44824.13</v>
       </c>
       <c r="H390" t="n">
-        <v>18541.69</v>
+        <v>48595.26</v>
       </c>
       <c r="I390" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J390" t="n">
+        <v>46</v>
+      </c>
+      <c r="K390" t="n">
         <v>6</v>
       </c>
-      <c r="K390" t="n">
-        <v>90</v>
-      </c>
       <c r="L390" t="n">
-        <v>0.2305</v>
+        <v>0.2364</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
-        <v>45637</v>
+        <v>46149</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
-        <v>45642</v>
+        <v>46152</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
-        <v>45642</v>
+        <v>46153</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
-        <v>45644</v>
+        <v>46154</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
-        <v>45645</v>
+        <v>46155</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
-        <v>45647</v>
+        <v>46156</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
-        <v>45653</v>
+        <v>46160</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
@@ -19492,55 +19492,55 @@
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
-        <v>45654</v>
+        <v>46161</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Clinical Products</t>
+          <t>Patient Care</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>LabReady Pro</t>
+          <t>NutriSupport Kit</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Alice Santos</t>
+          <t>Henrique Silva</t>
         </is>
       </c>
       <c r="G398" t="n">
-        <v>106332.84</v>
+        <v>41879.42</v>
       </c>
       <c r="H398" t="n">
-        <v>99812.95</v>
+        <v>46486.88</v>
       </c>
       <c r="I398" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="J398" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K398" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="L398" t="n">
-        <v>0.0238</v>
+        <v>0.2074</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
-        <v>45654</v>
+        <v>46161</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
@@ -19549,50 +19549,50 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Clinical Products</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>FlexCath Pro</t>
+          <t>LabReady Pro</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Gabriela Rocha</t>
+          <t>Alice Santos</t>
         </is>
       </c>
       <c r="G399" t="n">
-        <v>39026.92</v>
+        <v>106332.84</v>
       </c>
       <c r="H399" t="n">
-        <v>44291.93</v>
+        <v>99812.95</v>
       </c>
       <c r="I399" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J399" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K399" t="n">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="L399" t="n">
-        <v>0.0057</v>
+        <v>0.0238</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
-        <v>45654</v>
+        <v>46161</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -19602,41 +19602,41 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Patient Care</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>NutriSupport Kit</t>
+          <t>FlexCath Pro</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Henrique Silva</t>
+          <t>Gabriela Rocha</t>
         </is>
       </c>
       <c r="G400" t="n">
-        <v>41879.42</v>
+        <v>39026.92</v>
       </c>
       <c r="H400" t="n">
-        <v>46486.88</v>
+        <v>44291.93</v>
       </c>
       <c r="I400" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="J400" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K400" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L400" t="n">
-        <v>0.2074</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
-        <v>45655</v>
+        <v>46162</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
